--- a/diseases/d051/2015-2019.xlsx
+++ b/diseases/d051/2015-2019.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>1</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.01824911594438947</v>
       </c>
@@ -1309,9 +1306,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1705,9 +1699,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -2101,9 +2092,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2497,9 +2485,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2893,9 +2878,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -3289,9 +3271,6 @@
       <c r="O15" t="n">
         <v>1</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.01824911594438947</v>
       </c>
@@ -3981,9 +3960,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -4525,9 +4501,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4673,9 +4646,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -5365,9 +5335,6 @@
       <c r="O27" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.01819680904395967</v>
       </c>
@@ -5909,9 +5876,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6057,9 +6021,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -6897,9 +6858,6 @@
       <c r="O36" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.01819680904395967</v>
       </c>
@@ -7441,9 +7399,6 @@
       <c r="O39" t="n">
         <v>1</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.00194939985678539</v>
       </c>
@@ -7589,9 +7544,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -8725,9 +8677,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -9417,9 +9366,6 @@
       <c r="O51" t="n">
         <v>1</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.00194939985678539</v>
       </c>
@@ -9565,9 +9511,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -10701,9 +10644,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -11245,9 +11185,6 @@
       <c r="O62" t="n">
         <v>2</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.00389879971357078</v>
       </c>
@@ -11393,9 +11330,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -12677,9 +12611,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -13221,9 +13152,6 @@
       <c r="O74" t="n">
         <v>1</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.00194939985678539</v>
       </c>
@@ -13369,9 +13297,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -14653,9 +14578,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -15345,9 +15267,6 @@
       <c r="O87" t="n">
         <v>3</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.00584819957035617</v>
       </c>
@@ -15493,9 +15412,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -16777,9 +16693,6 @@
       <c r="O96" t="n">
         <v>2</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.03639361808791934</v>
       </c>
@@ -17321,9 +17234,6 @@
       <c r="O99" t="n">
         <v>2</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.00389879971357078</v>
       </c>
@@ -17469,9 +17379,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -18753,9 +18660,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -19297,9 +19201,6 @@
       <c r="O111" t="n">
         <v>3</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.00584819957035617</v>
       </c>
@@ -19445,9 +19346,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -20877,9 +20775,6 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
@@ -21421,9 +21316,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -21569,9 +21461,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -22853,9 +22742,6 @@
       <c r="O133" t="n">
         <v>2</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.03639361808791934</v>
       </c>
@@ -23397,9 +23283,6 @@
       <c r="O136" t="n">
         <v>2</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.00389879971357078</v>
       </c>
@@ -23545,9 +23428,6 @@
       <c r="O137" t="n">
         <v>1</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.01909861051878893</v>
       </c>
@@ -24681,9 +24561,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -25225,9 +25102,6 @@
       <c r="O147" t="n">
         <v>1</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0.00194939985678539</v>
       </c>
@@ -25373,9 +25247,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -26657,9 +26528,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -27201,9 +27069,6 @@
       <c r="O159" t="n">
         <v>1</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.001942265365676467</v>
       </c>
@@ -27349,9 +27214,6 @@
       <c r="O160" t="n">
         <v>3</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.05685261102722718</v>
       </c>
@@ -28337,9 +28199,6 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
@@ -28881,9 +28740,6 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0</v>
       </c>
@@ -29029,9 +28885,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -30017,9 +29870,6 @@
       <c r="O176" t="n">
         <v>0</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0</v>
       </c>
@@ -30561,9 +30411,6 @@
       <c r="O179" t="n">
         <v>1</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0.001942265365676467</v>
       </c>
@@ -30709,9 +30556,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -31845,9 +31689,6 @@
       <c r="O187" t="n">
         <v>0</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0</v>
       </c>
@@ -32389,9 +32230,6 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
@@ -32537,9 +32375,6 @@
       <c r="O191" t="n">
         <v>1</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0.01895087034240906</v>
       </c>
@@ -33673,9 +33508,6 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
@@ -34217,9 +34049,6 @@
       <c r="O201" t="n">
         <v>1</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0.001942265365676467</v>
       </c>
@@ -34365,9 +34194,6 @@
       <c r="O202" t="n">
         <v>0</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0</v>
       </c>
@@ -35353,9 +35179,6 @@
       <c r="O208" t="n">
         <v>0</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0</v>
       </c>
@@ -35897,9 +35720,6 @@
       <c r="O211" t="n">
         <v>1</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0.001942265365676467</v>
       </c>
@@ -36045,9 +35865,6 @@
       <c r="O212" t="n">
         <v>1</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0.01895087034240906</v>
       </c>
@@ -37181,9 +36998,6 @@
       <c r="O219" t="n">
         <v>1</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>0.01815410511517327</v>
       </c>
@@ -37725,9 +37539,6 @@
       <c r="O222" t="n">
         <v>0</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0</v>
       </c>
@@ -37873,9 +37684,6 @@
       <c r="O223" t="n">
         <v>0</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0</v>
       </c>
@@ -39009,9 +38817,6 @@
       <c r="O230" t="n">
         <v>0</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0</v>
       </c>
@@ -39553,9 +39358,6 @@
       <c r="O233" t="n">
         <v>2</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0.003884530731352934</v>
       </c>
@@ -39701,9 +39503,6 @@
       <c r="O234" t="n">
         <v>0</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0</v>
       </c>
@@ -40689,9 +40488,6 @@
       <c r="O240" t="n">
         <v>0</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0</v>
       </c>
@@ -41381,9 +41177,6 @@
       <c r="O244" t="n">
         <v>1</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0.001942265365676467</v>
       </c>
@@ -41529,9 +41322,6 @@
       <c r="O245" t="n">
         <v>0</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0</v>
       </c>
@@ -42665,9 +42455,6 @@
       <c r="O252" t="n">
         <v>0</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0</v>
       </c>
@@ -43209,9 +42996,6 @@
       <c r="O255" t="n">
         <v>1</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0.001942265365676467</v>
       </c>
@@ -43357,9 +43141,6 @@
       <c r="O256" t="n">
         <v>0</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0</v>
       </c>
@@ -44345,9 +44126,6 @@
       <c r="O262" t="n">
         <v>0</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0</v>
       </c>
@@ -44889,9 +44667,6 @@
       <c r="O265" t="n">
         <v>1</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0.001942265365676467</v>
       </c>
@@ -45037,9 +44812,6 @@
       <c r="O266" t="n">
         <v>0</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>0</v>
       </c>
@@ -46025,9 +45797,6 @@
       <c r="O272" t="n">
         <v>1</v>
       </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
       <c r="R272" t="n">
         <v>0.01815410511517327</v>
       </c>
@@ -46717,9 +46486,6 @@
       <c r="O276" t="n">
         <v>2</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0.003884530731352934</v>
       </c>
@@ -46865,9 +46631,6 @@
       <c r="O277" t="n">
         <v>0</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>0</v>
       </c>
@@ -48149,9 +47912,6 @@
       <c r="O285" t="n">
         <v>0</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0</v>
       </c>
@@ -48693,9 +48453,6 @@
       <c r="O288" t="n">
         <v>0</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0</v>
       </c>
@@ -49581,9 +49338,6 @@
       <c r="O294" t="n">
         <v>0</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>0</v>
       </c>
@@ -50125,9 +49879,6 @@
       <c r="O297" t="n">
         <v>0</v>
       </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
       <c r="R297" t="n">
         <v>0</v>
       </c>
@@ -51013,9 +50764,6 @@
       <c r="O303" t="n">
         <v>0</v>
       </c>
-      <c r="Q303" t="n">
-        <v>0</v>
-      </c>
       <c r="R303" t="n">
         <v>0</v>
       </c>
@@ -51557,9 +51305,6 @@
       <c r="O306" t="n">
         <v>0</v>
       </c>
-      <c r="Q306" t="n">
-        <v>0</v>
-      </c>
       <c r="R306" t="n">
         <v>0</v>
       </c>
@@ -52593,9 +52338,6 @@
       <c r="O313" t="n">
         <v>0</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="R313" t="n">
         <v>0</v>
       </c>
@@ -53137,9 +52879,6 @@
       <c r="O316" t="n">
         <v>0</v>
       </c>
-      <c r="Q316" t="n">
-        <v>0</v>
-      </c>
       <c r="R316" t="n">
         <v>0</v>
       </c>
@@ -54025,9 +53764,6 @@
       <c r="O322" t="n">
         <v>0</v>
       </c>
-      <c r="Q322" t="n">
-        <v>0</v>
-      </c>
       <c r="R322" t="n">
         <v>0</v>
       </c>
@@ -54569,9 +54305,6 @@
       <c r="O325" t="n">
         <v>0</v>
       </c>
-      <c r="Q325" t="n">
-        <v>0</v>
-      </c>
       <c r="R325" t="n">
         <v>0</v>
       </c>
@@ -55457,9 +55190,6 @@
       <c r="O331" t="n">
         <v>0</v>
       </c>
-      <c r="Q331" t="n">
-        <v>0</v>
-      </c>
       <c r="R331" t="n">
         <v>0</v>
       </c>
@@ -56149,9 +55879,6 @@
       <c r="O335" t="n">
         <v>0</v>
       </c>
-      <c r="Q335" t="n">
-        <v>0</v>
-      </c>
       <c r="R335" t="n">
         <v>0</v>
       </c>
@@ -57037,9 +56764,6 @@
       <c r="O341" t="n">
         <v>0</v>
       </c>
-      <c r="Q341" t="n">
-        <v>0</v>
-      </c>
       <c r="R341" t="n">
         <v>0</v>
       </c>
@@ -57581,9 +57305,6 @@
       <c r="O344" t="n">
         <v>2</v>
       </c>
-      <c r="Q344" t="n">
-        <v>0</v>
-      </c>
       <c r="R344" t="n">
         <v>0.00387289964422382</v>
       </c>
@@ -58617,9 +58338,6 @@
       <c r="O351" t="n">
         <v>0</v>
       </c>
-      <c r="Q351" t="n">
-        <v>0</v>
-      </c>
       <c r="R351" t="n">
         <v>0</v>
       </c>
@@ -59161,9 +58879,6 @@
       <c r="O354" t="n">
         <v>0</v>
       </c>
-      <c r="Q354" t="n">
-        <v>0</v>
-      </c>
       <c r="R354" t="n">
         <v>0</v>
       </c>
@@ -60197,9 +59912,6 @@
       <c r="O361" t="n">
         <v>0</v>
       </c>
-      <c r="Q361" t="n">
-        <v>0</v>
-      </c>
       <c r="R361" t="n">
         <v>0</v>
       </c>
@@ -60741,9 +60453,6 @@
       <c r="O364" t="n">
         <v>0</v>
       </c>
-      <c r="Q364" t="n">
-        <v>0</v>
-      </c>
       <c r="R364" t="n">
         <v>0</v>
       </c>
@@ -61777,9 +61486,6 @@
       <c r="O371" t="n">
         <v>0</v>
       </c>
-      <c r="Q371" t="n">
-        <v>0</v>
-      </c>
       <c r="R371" t="n">
         <v>0</v>
       </c>
@@ -62321,9 +62027,6 @@
       <c r="O374" t="n">
         <v>0</v>
       </c>
-      <c r="Q374" t="n">
-        <v>0</v>
-      </c>
       <c r="R374" t="n">
         <v>0</v>
       </c>
@@ -63209,9 +62912,6 @@
       <c r="O380" t="n">
         <v>0</v>
       </c>
-      <c r="Q380" t="n">
-        <v>0</v>
-      </c>
       <c r="R380" t="n">
         <v>0</v>
       </c>
@@ -63753,9 +63453,6 @@
       <c r="O383" t="n">
         <v>1</v>
       </c>
-      <c r="Q383" t="n">
-        <v>0</v>
-      </c>
       <c r="R383" t="n">
         <v>0.00193644982211191</v>
       </c>
@@ -64937,9 +64634,6 @@
       <c r="O391" t="n">
         <v>0</v>
       </c>
-      <c r="Q391" t="n">
-        <v>0</v>
-      </c>
       <c r="R391" t="n">
         <v>0</v>
       </c>
@@ -65481,9 +65175,6 @@
       <c r="O394" t="n">
         <v>0</v>
       </c>
-      <c r="Q394" t="n">
-        <v>0</v>
-      </c>
       <c r="R394" t="n">
         <v>0</v>
       </c>
@@ -66369,9 +66060,6 @@
       <c r="O400" t="n">
         <v>0</v>
       </c>
-      <c r="Q400" t="n">
-        <v>0</v>
-      </c>
       <c r="R400" t="n">
         <v>0</v>
       </c>
@@ -66913,9 +66601,6 @@
       <c r="O403" t="n">
         <v>1</v>
       </c>
-      <c r="Q403" t="n">
-        <v>0</v>
-      </c>
       <c r="R403" t="n">
         <v>0.001931701002201251</v>
       </c>
@@ -67061,9 +66746,6 @@
       <c r="O404" t="n">
         <v>1</v>
       </c>
-      <c r="Q404" t="n">
-        <v>0</v>
-      </c>
       <c r="R404" t="n">
         <v>0.01869952122680827</v>
       </c>
@@ -68049,9 +67731,6 @@
       <c r="O410" t="n">
         <v>0</v>
       </c>
-      <c r="Q410" t="n">
-        <v>0</v>
-      </c>
       <c r="R410" t="n">
         <v>0</v>
       </c>
@@ -68741,9 +68420,6 @@
       <c r="O414" t="n">
         <v>0</v>
       </c>
-      <c r="Q414" t="n">
-        <v>0</v>
-      </c>
       <c r="R414" t="n">
         <v>0</v>
       </c>
@@ -68889,9 +68565,6 @@
       <c r="O415" t="n">
         <v>1</v>
       </c>
-      <c r="Q415" t="n">
-        <v>0</v>
-      </c>
       <c r="R415" t="n">
         <v>0.01869952122680827</v>
       </c>
@@ -69877,9 +69550,6 @@
       <c r="O421" t="n">
         <v>1</v>
       </c>
-      <c r="Q421" t="n">
-        <v>0</v>
-      </c>
       <c r="R421" t="n">
         <v>0.01811017105237661</v>
       </c>
@@ -70569,9 +70239,6 @@
       <c r="O425" t="n">
         <v>0</v>
       </c>
-      <c r="Q425" t="n">
-        <v>0</v>
-      </c>
       <c r="R425" t="n">
         <v>0</v>
       </c>
@@ -70717,9 +70384,6 @@
       <c r="O426" t="n">
         <v>0</v>
       </c>
-      <c r="Q426" t="n">
-        <v>0</v>
-      </c>
       <c r="R426" t="n">
         <v>0</v>
       </c>
@@ -71705,9 +71369,6 @@
       <c r="O432" t="n">
         <v>0</v>
       </c>
-      <c r="Q432" t="n">
-        <v>0</v>
-      </c>
       <c r="R432" t="n">
         <v>0</v>
       </c>
@@ -72249,9 +71910,6 @@
       <c r="O435" t="n">
         <v>0</v>
       </c>
-      <c r="Q435" t="n">
-        <v>0</v>
-      </c>
       <c r="R435" t="n">
         <v>0</v>
       </c>
@@ -72397,9 +72055,6 @@
       <c r="O436" t="n">
         <v>0</v>
       </c>
-      <c r="Q436" t="n">
-        <v>0</v>
-      </c>
       <c r="R436" t="n">
         <v>0</v>
       </c>
@@ -73385,9 +73040,6 @@
       <c r="O442" t="n">
         <v>0</v>
       </c>
-      <c r="Q442" t="n">
-        <v>0</v>
-      </c>
       <c r="R442" t="n">
         <v>0</v>
       </c>
@@ -73929,9 +73581,6 @@
       <c r="O445" t="n">
         <v>0</v>
       </c>
-      <c r="Q445" t="n">
-        <v>0</v>
-      </c>
       <c r="R445" t="n">
         <v>0</v>
       </c>
@@ -74077,9 +73726,6 @@
       <c r="O446" t="n">
         <v>0</v>
       </c>
-      <c r="Q446" t="n">
-        <v>0</v>
-      </c>
       <c r="R446" t="n">
         <v>0</v>
       </c>
@@ -75213,9 +74859,6 @@
       <c r="O453" t="n">
         <v>0</v>
       </c>
-      <c r="Q453" t="n">
-        <v>0</v>
-      </c>
       <c r="R453" t="n">
         <v>0</v>
       </c>
@@ -75757,9 +75400,6 @@
       <c r="O456" t="n">
         <v>0</v>
       </c>
-      <c r="Q456" t="n">
-        <v>0</v>
-      </c>
       <c r="R456" t="n">
         <v>0</v>
       </c>
@@ -75905,9 +75545,6 @@
       <c r="O457" t="n">
         <v>0</v>
       </c>
-      <c r="Q457" t="n">
-        <v>0</v>
-      </c>
       <c r="R457" t="n">
         <v>0</v>
       </c>
@@ -76893,9 +76530,6 @@
       <c r="O463" t="n">
         <v>0</v>
       </c>
-      <c r="Q463" t="n">
-        <v>0</v>
-      </c>
       <c r="R463" t="n">
         <v>0</v>
       </c>
@@ -77437,9 +77071,6 @@
       <c r="O466" t="n">
         <v>0</v>
       </c>
-      <c r="Q466" t="n">
-        <v>0</v>
-      </c>
       <c r="R466" t="n">
         <v>0</v>
       </c>
@@ -77585,9 +77216,6 @@
       <c r="O467" t="n">
         <v>0</v>
       </c>
-      <c r="Q467" t="n">
-        <v>0</v>
-      </c>
       <c r="R467" t="n">
         <v>0</v>
       </c>
@@ -78721,9 +78349,6 @@
       <c r="O474" t="n">
         <v>0</v>
       </c>
-      <c r="Q474" t="n">
-        <v>0</v>
-      </c>
       <c r="R474" t="n">
         <v>0</v>
       </c>
@@ -79265,9 +78890,6 @@
       <c r="O477" t="n">
         <v>1</v>
       </c>
-      <c r="Q477" t="n">
-        <v>0</v>
-      </c>
       <c r="R477" t="n">
         <v>0.001931701002201251</v>
       </c>
@@ -79413,9 +79035,6 @@
       <c r="O478" t="n">
         <v>0</v>
       </c>
-      <c r="Q478" t="n">
-        <v>0</v>
-      </c>
       <c r="R478" t="n">
         <v>0</v>
       </c>
@@ -80549,9 +80168,6 @@
       <c r="O485" t="n">
         <v>0</v>
       </c>
-      <c r="Q485" t="n">
-        <v>0</v>
-      </c>
       <c r="R485" t="n">
         <v>0</v>
       </c>
@@ -81093,9 +80709,6 @@
       <c r="O488" t="n">
         <v>1</v>
       </c>
-      <c r="Q488" t="n">
-        <v>0</v>
-      </c>
       <c r="R488" t="n">
         <v>0.001931701002201251</v>
       </c>
@@ -81241,9 +80854,6 @@
       <c r="O489" t="n">
         <v>0</v>
       </c>
-      <c r="Q489" t="n">
-        <v>0</v>
-      </c>
       <c r="R489" t="n">
         <v>0</v>
       </c>
@@ -82377,9 +81987,6 @@
       <c r="O496" t="n">
         <v>0</v>
       </c>
-      <c r="Q496" t="n">
-        <v>0</v>
-      </c>
       <c r="R496" t="n">
         <v>0</v>
       </c>
@@ -82921,9 +82528,6 @@
       <c r="O499" t="n">
         <v>0</v>
       </c>
-      <c r="Q499" t="n">
-        <v>0</v>
-      </c>
       <c r="R499" t="n">
         <v>0</v>
       </c>
@@ -83069,9 +82673,6 @@
       <c r="O500" t="n">
         <v>0</v>
       </c>
-      <c r="Q500" t="n">
-        <v>0</v>
-      </c>
       <c r="R500" t="n">
         <v>0</v>
       </c>
@@ -84057,9 +83658,6 @@
       <c r="O506" t="n">
         <v>0</v>
       </c>
-      <c r="Q506" t="n">
-        <v>0</v>
-      </c>
       <c r="R506" t="n">
         <v>0</v>
       </c>
@@ -84749,9 +84347,6 @@
       <c r="O510" t="n">
         <v>0</v>
       </c>
-      <c r="Q510" t="n">
-        <v>0</v>
-      </c>
       <c r="R510" t="n">
         <v>0</v>
       </c>
@@ -84897,9 +84492,6 @@
       <c r="O511" t="n">
         <v>0</v>
       </c>
-      <c r="Q511" t="n">
-        <v>0</v>
-      </c>
       <c r="R511" t="n">
         <v>0</v>
       </c>
@@ -85885,9 +85477,6 @@
       <c r="O517" t="n">
         <v>1</v>
       </c>
-      <c r="Q517" t="n">
-        <v>0</v>
-      </c>
       <c r="R517" t="n">
         <v>0.01811017105237661</v>
       </c>
@@ -86429,9 +86018,6 @@
       <c r="O520" t="n">
         <v>0</v>
       </c>
-      <c r="Q520" t="n">
-        <v>0</v>
-      </c>
       <c r="R520" t="n">
         <v>0</v>
       </c>
@@ -86575,9 +86161,6 @@
         <v>0</v>
       </c>
       <c r="O521" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q521" t="n">
         <v>0</v>
       </c>
       <c r="R521" t="n">
